--- a/temp/pages/StructureDefinition-botswana-amr-susceptibility-observation.xlsx
+++ b/temp/pages/StructureDefinition-botswana-amr-susceptibility-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="519">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-susceptibility-observation</t>
+    <t>http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-susceptibility-observation</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T10:14:37-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Records S/I/R (and optional MIC) for a single antibiotic test on a specimen</t>
+    <t>Records S/I/R (and optional MIC) for a single antibiotic test on a specimen. Should be referenced from the parent OrganismObservation via hasMember.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}bw-amr-2:If there is no value and no interpretation, a dataAbsentReason must be provided {value.exists() or interpretation.exists() or dataAbsentReason.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -339,22 +339,110 @@
 </t>
   </si>
   <si>
-    <t>Observation.meta.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.meta.extension</t>
+    <t>Observation.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Observation.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>IETF language tag</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Observation.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Observation.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Observation.extension</t>
   </si>
   <si>
     <t>extensions
@@ -368,10 +456,530 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business Identifier for observation</t>
+  </si>
+  <si>
+    <t>A unique identifier assigned to this observation.</t>
+  </si>
+  <si>
+    <t>Allows observations to be distinguished and referenced.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Observation.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|4.3.0|DeviceRequest|4.3.0|ImmunizationRecommendation|4.3.0|MedicationRequest|4.3.0|NutritionOrder|4.3.0|ServiceRequest|4.3.0)
+</t>
+  </si>
+  <si>
+    <t>Fulfills plan, proposal or order</t>
+  </si>
+  <si>
+    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+  </si>
+  <si>
+    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
+  </si>
+  <si>
+    <t>Event.basedOn</t>
+  </si>
+  <si>
+    <t>ORC</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Observation.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Container
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(MedicationAdministration|4.3.0|MedicationDispense|4.3.0|MedicationStatement|4.3.0|Procedure|4.3.0|Immunization|4.3.0|ImagingStudy|4.3.0)
+</t>
+  </si>
+  <si>
+    <t>Part of referenced event</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+  </si>
+  <si>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+  </si>
+  <si>
+    <t>Event.partOf</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>Observation.status</t>
+  </si>
+  <si>
+    <t>registered | preliminary | final | amended +</t>
+  </si>
+  <si>
+    <t>The status of the result value.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
+    <t>final</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Codes providing the status of an observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>&lt; 445584004 |Report by finality status|</t>
+  </si>
+  <si>
+    <t>OBX-11</t>
+  </si>
+  <si>
+    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Observation.category</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Classification of  type of observation</t>
+  </si>
+  <si>
+    <t>A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.3.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:laboratory</t>
+  </si>
+  <si>
+    <t>laboratory</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
+    &lt;code value="laboratory"/&gt;
+    &lt;display value="Laboratory"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.category:microbiologyStudies</t>
+  </si>
+  <si>
+    <t>microbiologyStudies</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="18725-2"/&gt;
+    &lt;display value="Microbiology studies (set)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name
+</t>
+  </si>
+  <si>
+    <t>Type of observation (code / type)</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-antibiotic-susceptibility-loinc</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-patient)
+</t>
+  </si>
+  <si>
+    <t>Who and/or what the observation is about</t>
+  </si>
+  <si>
+    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+  </si>
+  <si>
+    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
+  </si>
+  <si>
+    <t>Observations have no value if you don't know who or what they're about.</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>participation[typeCode=RTGT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource|4.3.0)
+</t>
+  </si>
+  <si>
+    <t>What the observation is about, when it is not about the subject of record</t>
+  </si>
+  <si>
+    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
+  </si>
+  <si>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>Observation.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter|4.3.0)
+</t>
+  </si>
+  <si>
+    <t>Healthcare event during which this observation is made</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
+  </si>
+  <si>
+    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occurrence
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Clinically relevant time/time-period for observation</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+  </si>
+  <si>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+  </si>
+  <si>
+    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>Date/Time this version was made available</t>
+  </si>
+  <si>
+    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
+  </si>
+  <si>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Observation.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.3.0|PractitionerRole|4.3.0|Organization|4.3.0|CareTeam|4.3.0|Patient|4.3.0|RelatedPerson|4.3.0)
+</t>
+  </si>
+  <si>
+    <t>Who is responsible for the observation</t>
+  </si>
+  <si>
+    <t>Who was responsible for asserting the observed value as "true".</t>
+  </si>
+  <si>
+    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+  </si>
+  <si>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-7
+</t>
+  </si>
+  <si>
+    <t>&lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>OBX.2, OBX.5, OBX.6</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].extension</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -381,686 +989,148 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Observation.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
+    <t>Observation.value[x]:valueQuantity.value</t>
+  </si>
+  <si>
+    <t>Observation.value[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
 </t>
   </si>
   <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Observation.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.comparator</t>
+  </si>
+  <si>
+    <t>Observation.value[x].comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.3.0</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x].unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x].system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>http://unitsofmeasure.org</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
 </t>
   </si>
   <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>http://bw.health.gov/fhir/StructureDefinition/BotswanaAMR-SusceptibilityObservation</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>Observation.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Observation.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Observation.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>IETF language tag</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Observation.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Observation.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Observation.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Observation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Business Identifier for observation</t>
-  </si>
-  <si>
-    <t>A unique identifier assigned to this observation.</t>
-  </si>
-  <si>
-    <t>Allows observations to be distinguished and referenced.</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>OBX.21  For OBX segments from systems without OBX-21 support a combination of ORC/OBR and OBX must be negotiated between trading partners to uniquely identify the OBX segment. Depending on how V2 has been implemented each of these may be an option: 1) OBR-3 + OBX-3 + OBX-4 or 2) OBR-3 + OBR-4 + OBX-3 + OBX-4 or 2) some other way to uniquely ID the OBR/ORC + OBX-3 + OBX-4.</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Observation.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
-</t>
-  </si>
-  <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
-  </si>
-  <si>
-    <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
-  </si>
-  <si>
-    <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>ORC</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Observation.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Container
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
-</t>
-  </si>
-  <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
-  </si>
-  <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
-  </si>
-  <si>
-    <t>Event.partOf</t>
-  </si>
-  <si>
-    <t>Varies by domain</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>Observation.status</t>
-  </si>
-  <si>
-    <t>registered | preliminary | final | amended +</t>
-  </si>
-  <si>
-    <t>The status of the result value.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
-  </si>
-  <si>
-    <t>final</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Codes providing the status of an observation.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>&lt; 445584004 |Report by finality status|</t>
-  </si>
-  <si>
-    <t>OBX-11</t>
-  </si>
-  <si>
-    <t>status  Amended &amp; Final are differentiated by whether it is the subject of a ControlAct event with a type of "revise"</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Observation.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
-  </si>
-  <si>
-    <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
-  </si>
-  <si>
-    <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name
-</t>
-  </si>
-  <si>
-    <t>Type of observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-antibiotic-susceptibility-loinc</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-patient)
-</t>
-  </si>
-  <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
-  </si>
-  <si>
-    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
-  </si>
-  <si>
-    <t>Observations have no value if you don't know who or what they're about.</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>participation[typeCode=RTGT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Observation.focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
-    <t>What the observation is about, when it is not about the subject of record</t>
-  </si>
-  <si>
-    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
-  </si>
-  <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>Observation.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter)
-</t>
-  </si>
-  <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
-  </si>
-  <si>
-    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
-  </si>
-  <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectiveDateTime</t>
-  </si>
-  <si>
-    <t>effectiveDateTime</t>
-  </si>
-  <si>
-    <t>Observation.issued</t>
-  </si>
-  <si>
-    <t>Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
-  </si>
-  <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.value[x]</t>
-  </si>
-  <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-7
-</t>
-  </si>
-  <si>
-    <t>&lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>OBX.2, OBX.5, OBX.6</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1079,10 +1149,13 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.3.0</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1111,7 +1184,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-interpretation</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1164,10 +1237,13 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.3.0</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1197,10 +1273,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-ast-method-vs</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1212,7 +1285,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-specimen)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-specimen)
 </t>
   </si>
   <si>
@@ -1240,7 +1313,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.3.0|DeviceMetric|4.3.0)
 </t>
   </si>
   <si>
@@ -1297,10 +1370,6 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.extension</t>
   </si>
   <si>
@@ -1324,7 +1393,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.3.0}
 </t>
   </si>
   <si>
@@ -1374,7 +1443,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.3.0</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1407,7 +1476,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.3.0</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1444,7 +1513,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.3.0|QuestionnaireResponse|4.3.0|MolecularSequence|4.3.0)
 </t>
   </si>
   <si>
@@ -1466,7 +1535,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-organism-observation)
+    <t xml:space="preserve">Reference(DocumentReference|4.3.0|ImagingStudy|4.3.0|Media|4.3.0|QuestionnaireResponse|4.3.0|Observation|4.3.0|MolecularSequence|4.3.0)
 </t>
   </si>
   <si>
@@ -1531,7 +1600,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.3.0</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1569,7 +1638,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.3.0</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -1880,12 +1949,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP61"/>
+  <dimension ref="A1:AP62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.0546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.80078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.69921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.265625" customWidth="true" bestFit="true"/>
@@ -1893,7 +1962,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.09375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1908,7 +1977,7 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="55.359375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="93.34765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.4609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
@@ -2434,21 +2503,23 @@
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>20</v>
@@ -2497,7 +2568,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
@@ -2509,7 +2580,7 @@
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2521,7 +2592,7 @@
         <v>20</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>20</v>
@@ -2532,21 +2603,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2593,28 +2664,28 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>120</v>
@@ -2623,13 +2694,13 @@
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2641,7 +2712,7 @@
         <v>20</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>20</v>
@@ -2652,14 +2723,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2675,19 +2746,19 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2737,7 +2808,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2761,7 +2832,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -2772,21 +2843,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2795,19 +2866,19 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2857,19 +2928,19 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>20</v>
@@ -2881,7 +2952,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -2892,21 +2963,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2915,19 +2986,19 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2977,19 +3048,19 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3001,7 +3072,7 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>20</v>
@@ -3012,14 +3083,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3032,24 +3103,26 @@
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O10" s="2"/>
+      <c r="O10" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -3058,7 +3131,7 @@
         <v>20</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>144</v>
+        <v>20</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>20</v>
@@ -3097,7 +3170,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3109,7 +3182,7 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3121,7 +3194,7 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>20</v>
@@ -3132,10 +3205,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3158,18 +3231,18 @@
         <v>94</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -3193,29 +3266,31 @@
         <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="Y11" s="2"/>
-      <c r="Z11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3230,19 +3305,19 @@
         <v>105</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>20</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>20</v>
@@ -3250,14 +3325,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3276,18 +3351,18 @@
         <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
       </c>
@@ -3311,11 +3386,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -3348,16 +3425,16 @@
         <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -3368,42 +3445,42 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3453,13 +3530,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -3468,16 +3545,16 @@
         <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>20</v>
@@ -3488,10 +3565,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3499,7 +3576,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
@@ -3508,24 +3585,26 @@
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3534,7 +3613,7 @@
         <v>20</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>20</v>
@@ -3549,13 +3628,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3573,10 +3652,10 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -3588,19 +3667,19 @@
         <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>20</v>
+        <v>190</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>20</v>
+        <v>191</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>20</v>
@@ -3608,21 +3687,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3634,18 +3713,20 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -3669,37 +3750,35 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
@@ -3717,10 +3796,10 @@
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>20</v>
@@ -3728,21 +3807,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -3754,18 +3835,20 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3774,7 +3857,7 @@
         <v>20</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>20</v>
@@ -3789,13 +3872,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3813,7 +3896,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3825,7 +3908,7 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -3837,10 +3920,10 @@
         <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -3848,21 +3931,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="D17" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3874,18 +3959,20 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
       </c>
@@ -3894,7 +3981,7 @@
         <v>20</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>20</v>
@@ -3909,13 +3996,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>20</v>
+        <v>199</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3933,7 +4020,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3945,7 +4032,7 @@
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3957,10 +4044,10 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>20</v>
+        <v>204</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>20</v>
@@ -3968,45 +4055,45 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J18" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K18" t="s" s="2">
-        <v>113</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4031,13 +4118,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4055,45 +4140,45 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>20</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4101,10 +4186,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4116,17 +4201,19 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4175,13 +4262,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -4190,19 +4277,19 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>20</v>
@@ -4210,14 +4297,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4236,18 +4323,18 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
       </c>
@@ -4295,7 +4382,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4310,19 +4397,19 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -4330,21 +4417,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4356,18 +4443,20 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
       </c>
@@ -4415,13 +4504,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -4430,19 +4519,19 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4450,14 +4539,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4470,25 +4559,25 @@
         <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>167</v>
+        <v>253</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4498,7 +4587,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>232</v>
+        <v>20</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -4513,34 +4602,32 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>233</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>235</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>93</v>
@@ -4552,19 +4639,19 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4572,21 +4659,23 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -4595,22 +4684,22 @@
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4635,13 +4724,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>247</v>
+        <v>20</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4659,13 +4748,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4674,19 +4763,19 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4694,18 +4783,18 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>93</v>
@@ -4720,20 +4809,18 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4757,11 +4844,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4779,10 +4868,10 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>93</v>
@@ -4794,30 +4883,30 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>258</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>259</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>263</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4825,10 +4914,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4840,19 +4929,17 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4901,13 +4988,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -4916,19 +5003,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -4936,10 +5023,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4950,7 +5037,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4962,18 +5049,20 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -5009,28 +5098,26 @@
         <v>20</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>105</v>
@@ -5039,31 +5126,33 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>281</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5082,19 +5171,19 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5143,7 +5232,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5152,44 +5241,44 @@
         <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>287</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
@@ -5201,23 +5290,19 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>293</v>
+        <v>95</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -5253,17 +5338,19 @@
         <v>20</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>299</v>
+        <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5275,22 +5362,22 @@
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>302</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>20</v>
@@ -5298,23 +5385,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="B29" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>305</v>
-      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>292</v>
+        <v>139</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5323,23 +5408,21 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>293</v>
+        <v>140</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>294</v>
+        <v>141</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5375,46 +5458,46 @@
         <v>20</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>20</v>
+        <v>306</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>20</v>
+        <v>307</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>302</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>20</v>
@@ -5422,10 +5505,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5448,18 +5531,20 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>128</v>
+        <v>311</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5507,7 +5592,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5528,13 +5613,13 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>20</v>
@@ -5542,10 +5627,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5556,34 +5641,36 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>314</v>
+        <v>113</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="Q31" s="2"/>
+      <c r="Q31" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="R31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5603,13 +5690,11 @@
         <v>20</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>20</v>
+        <v>325</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>20</v>
@@ -5627,13 +5712,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -5642,19 +5727,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>318</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>20</v>
@@ -5662,10 +5747,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5688,19 +5773,17 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5737,17 +5820,19 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5756,7 +5841,7 @@
         <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>105</v>
@@ -5765,31 +5850,29 @@
         <v>20</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>329</v>
+        <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5810,19 +5893,17 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>335</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5832,7 +5913,7 @@
         <v>20</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>20</v>
@@ -5871,7 +5952,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5880,7 +5961,7 @@
         <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>105</v>
@@ -5889,27 +5970,27 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>329</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5929,22 +6010,22 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>242</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5969,13 +6050,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>341</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5993,7 +6074,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6002,7 +6083,7 @@
         <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>105</v>
@@ -6014,10 +6095,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>191</v>
+        <v>336</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6028,18 +6109,18 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>346</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
@@ -6054,19 +6135,19 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6091,11 +6172,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6113,16 +6196,16 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>105</v>
@@ -6131,38 +6214,38 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>353</v>
+        <v>137</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6174,19 +6257,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>357</v>
+        <v>194</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6211,13 +6294,11 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6235,7 +6316,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6253,27 +6334,27 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>20</v>
+        <v>372</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>20</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6284,7 +6365,7 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6296,18 +6377,20 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>242</v>
+        <v>377</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6331,13 +6414,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>369</v>
+        <v>20</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6355,13 +6438,13 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
@@ -6373,27 +6456,27 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>370</v>
+        <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>373</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6416,20 +6499,18 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6453,13 +6534,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>158</v>
+        <v>388</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6477,7 +6558,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6495,27 +6576,27 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>20</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6523,7 +6604,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
@@ -6538,18 +6619,20 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>384</v>
+        <v>194</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6573,13 +6656,11 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>20</v>
@@ -6597,7 +6678,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6615,27 +6696,27 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>388</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>391</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6643,7 +6724,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
@@ -6658,16 +6739,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6717,7 +6798,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6735,27 +6816,27 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6766,7 +6847,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6778,20 +6859,18 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6839,45 +6918,45 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>407</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>20</v>
+        <v>417</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>20</v>
+        <v>420</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6888,7 +6967,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6900,16 +6979,20 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>107</v>
+        <v>423</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6957,19 +7040,19 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>109</v>
+        <v>421</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>20</v>
+        <v>427</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
@@ -6978,10 +7061,10 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>20</v>
+        <v>428</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>110</v>
+        <v>429</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -6992,21 +7075,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7018,17 +7101,15 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>113</v>
+        <v>331</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>114</v>
+        <v>299</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>116</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -7077,19 +7158,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>120</v>
+        <v>301</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7101,7 +7182,7 @@
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>110</v>
+        <v>302</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7112,14 +7193,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>414</v>
+        <v>139</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7132,26 +7213,24 @@
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>415</v>
+        <v>141</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>416</v>
+        <v>305</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
       </c>
@@ -7199,7 +7278,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>417</v>
+        <v>308</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7211,7 +7290,7 @@
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7223,7 +7302,7 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>191</v>
+        <v>302</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7234,42 +7313,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>419</v>
+        <v>140</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
       </c>
@@ -7317,19 +7400,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>422</v>
+        <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7338,10 +7421,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>424</v>
+        <v>137</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7352,10 +7435,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7378,13 +7461,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7435,7 +7518,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7444,7 +7527,7 @@
         <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>105</v>
@@ -7456,10 +7539,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7470,10 +7553,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7496,20 +7579,16 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>242</v>
+        <v>438</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7533,13 +7612,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>435</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7557,7 +7636,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7566,7 +7645,7 @@
         <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>105</v>
@@ -7575,13 +7654,13 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>436</v>
+        <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>354</v>
+        <v>447</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7592,10 +7671,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7606,7 +7685,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7618,19 +7697,19 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7655,13 +7734,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7679,13 +7758,13 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
@@ -7697,13 +7776,13 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7714,10 +7793,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7728,7 +7807,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7740,17 +7819,19 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>446</v>
+        <v>194</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7775,13 +7856,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>20</v>
+        <v>388</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>20</v>
+        <v>462</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>20</v>
+        <v>463</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7799,13 +7880,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7817,13 +7898,13 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>20</v>
+        <v>455</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>450</v>
+        <v>374</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7834,10 +7915,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7860,16 +7941,18 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>411</v>
+        <v>465</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
@@ -7917,7 +8000,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7938,10 +8021,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>423</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -7952,10 +8035,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7966,7 +8049,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -7975,20 +8058,18 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>456</v>
+        <v>331</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8037,13 +8118,13 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
@@ -8058,10 +8139,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8072,10 +8153,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8086,7 +8167,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8098,16 +8179,16 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8157,7 +8238,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8178,10 +8259,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8192,10 +8273,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8218,20 +8299,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>402</v>
+        <v>482</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>20</v>
       </c>
@@ -8279,7 +8358,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8291,7 +8370,7 @@
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>473</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8300,10 +8379,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8314,10 +8393,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8328,7 +8407,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8337,19 +8416,23 @@
         <v>20</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>107</v>
+        <v>488</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
       </c>
@@ -8397,19 +8480,19 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>109</v>
+        <v>487</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>20</v>
+        <v>492</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
@@ -8418,10 +8501,10 @@
         <v>20</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>20</v>
+        <v>493</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>110</v>
+        <v>494</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8432,21 +8515,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8458,17 +8541,15 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>113</v>
+        <v>331</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>114</v>
+        <v>299</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>116</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8517,19 +8598,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>120</v>
+        <v>301</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8541,7 +8622,7 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>110</v>
+        <v>302</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8552,14 +8633,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>414</v>
+        <v>139</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8572,26 +8653,24 @@
         <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>415</v>
+        <v>141</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>416</v>
+        <v>305</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -8639,7 +8718,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>417</v>
+        <v>308</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8651,7 +8730,7 @@
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8663,7 +8742,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>191</v>
+        <v>302</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8674,45 +8753,45 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>242</v>
+        <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>480</v>
+        <v>434</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>482</v>
+        <v>143</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>256</v>
+        <v>149</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8737,13 +8816,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>483</v>
+        <v>20</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>484</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8761,34 +8840,34 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>479</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>485</v>
+        <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>261</v>
+        <v>137</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -8796,10 +8875,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8807,7 +8886,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>93</v>
@@ -8822,19 +8901,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>323</v>
+        <v>194</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>327</v>
+        <v>216</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8859,13 +8938,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>20</v>
+        <v>388</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>20</v>
+        <v>502</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>20</v>
+        <v>503</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8883,10 +8962,10 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>93</v>
@@ -8901,27 +8980,27 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>330</v>
+        <v>220</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>331</v>
+        <v>221</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8941,22 +9020,22 @@
         <v>20</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>492</v>
+        <v>286</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8981,13 +9060,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>151</v>
+        <v>20</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>341</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9005,7 +9084,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9014,7 +9093,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9023,38 +9102,38 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>20</v>
+        <v>508</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>191</v>
+        <v>291</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>344</v>
+        <v>292</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>20</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>346</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9066,19 +9145,19 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>242</v>
+        <v>194</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>347</v>
+        <v>510</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>348</v>
+        <v>511</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>349</v>
+        <v>512</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9103,13 +9182,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>151</v>
+        <v>360</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>495</v>
+        <v>361</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>496</v>
+        <v>362</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9127,16 +9206,16 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9145,31 +9224,31 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>353</v>
+        <v>137</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>355</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9188,19 +9267,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>498</v>
+        <v>367</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>499</v>
+        <v>368</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>405</v>
+        <v>369</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9225,13 +9304,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>20</v>
+        <v>514</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>20</v>
+        <v>515</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -9249,7 +9328,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>497</v>
+        <v>513</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9267,18 +9346,140 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>20</v>
+        <v>372</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>408</v>
+        <v>373</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP61" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>20</v>
       </c>
     </row>
